--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0157.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0157.xlsx
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Này! Đó là anh ta!</t>
+          <t>Này! Đó là anh tao!</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Ta sẽ phải rời đi sau khi Trò Chơi Ven Sông kết thúc.</t>
+          <t>Tao sẽ phải rời đi sau khi Trò Chơi Ven Sông kết thúc.</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
